--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_355_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_355_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0375</v>
+        <v>14.0837</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1918</v>
+        <v>11.8011</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8457</v>
+        <v>2.2826</v>
       </c>
       <c r="G2" t="n">
         <v>9.7178</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.3428</v>
+        <v>-1.2966</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1949</v>
+        <v>-0.5856</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1479</v>
+        <v>-0.711</v>
       </c>
       <c r="V2" t="n">
         <v>4.9667</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5912</v>
+        <v>7.1513</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0777</v>
+        <v>4.6123</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5135</v>
+        <v>2.539</v>
       </c>
       <c r="G3" t="n">
         <v>4.5114</v>
@@ -688,13 +688,13 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0646</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1202</v>
+        <v>-0.5856</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0557</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>2.6805</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0544</v>
+        <v>4.3498</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325</v>
+        <v>1.7548</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7295</v>
+        <v>2.595</v>
       </c>
       <c r="G4" t="n">
         <v>2.1496</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9796</v>
+        <v>0.275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6018</v>
+        <v>0.0316</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3778</v>
+        <v>0.2434</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3943</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9081</v>
+        <v>1.2831</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2325</v>
+        <v>-0.1181</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3245</v>
+        <v>1.4013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8199</v>
+        <v>0.2694</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3447</v>
+        <v>-0.4801</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4752</v>
+        <v>0.7494</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5388</v>
+        <v>0.1373</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.0672</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9507</v>
+        <v>0.0701</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.719</v>
+        <v>0.1321</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2435</v>
+        <v>-0.5473</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4755</v>
+        <v>0.6793</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4453</v>
+        <v>-0.0738</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9972</v>
+        <v>0.1817</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6984</v>
+        <v>1.1679</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5348000000000001</v>
+        <v>2.4252</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2332</v>
+        <v>-1.2573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2694</v>
+        <v>0.8199</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4801</v>
+        <v>0.3447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7494</v>
+        <v>0.4752</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1373</v>
+        <v>2.5388</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0672</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0701</v>
+        <v>1.9507</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1321</v>
+        <v>-1.719</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5473</v>
+        <v>-0.2435</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6793</v>
+        <v>-1.4755</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6585</v>
+        <v>-1.1854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>-0.2555</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0136</v>
+        <v>-0.93</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4526</v>
+        <v>0.9574</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6964</v>
+        <v>1.9323</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2438</v>
+        <v>-0.975</v>
       </c>
       <c r="G7" t="n">
         <v>0.2762</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1457</v>
+        <v>-0.6409</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.847</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2196</v>
+        <v>0.4891</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4495</v>
+        <v>1.6854</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2299</v>
+        <v>-1.1963</v>
       </c>
       <c r="G8" t="n">
         <v>1.1383</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8465</v>
+        <v>-0.577</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0997</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0738</v>
+        <v>-0.6128</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1866</v>
+        <v>1.7148</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2604</v>
+        <v>-2.3276</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2556</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7486</v>
+        <v>-1.2876</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0351</v>
+        <v>-0.507</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7134</v>
+        <v>-0.7806</v>
       </c>
       <c r="V9" t="n">
         <v>2.0026</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5043</v>
+        <v>-0.9196</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7696</v>
+        <v>-1.3529</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2653</v>
+        <v>0.4333</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4052</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.1406</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.1061</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6013</v>
+        <v>-1.3079</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4221</v>
+        <v>-0.2295</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1792</v>
+        <v>-1.0784</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0474</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0179</v>
+        <v>-0.7244</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.4795</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3457</v>
+        <v>-0.2449</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6273</v>
+        <v>-1.6871</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2908</v>
+        <v>-2.2161</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6635</v>
+        <v>0.529</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8182</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0411</v>
+        <v>-1.1009</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>-0.8962</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0703</v>
+        <v>-0.2047</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8203</v>
+        <v>-3.7531</v>
       </c>
       <c r="E13" t="n">
         <v>-2.4353</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3851</v>
+        <v>-1.3178</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8681</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7925</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.3348</v>
+        <v>21.2018</v>
       </c>
       <c r="E14" t="n">
-        <v>17.7069</v>
+        <v>19.574</v>
       </c>
       <c r="F14" t="n">
-        <v>1.627799999999998</v>
+        <v>1.6278</v>
       </c>
       <c r="G14" t="n">
         <v>12.4881</v>
@@ -1546,13 +1546,13 @@
         <v>16.2366</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.8492</v>
+        <v>-7.982</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.602700000000001</v>
+        <v>-4.7359</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.2463</v>
+        <v>-3.2462</v>
       </c>
       <c r="V14" t="n">
         <v>8.5776</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0417</v>
+        <v>5.4806</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7085</v>
+        <v>5.4162</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3333</v>
+        <v>0.0644</v>
       </c>
       <c r="G15" t="n">
         <v>3.6802</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5033</v>
+        <v>1.9421</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2047</v>
+        <v>0.9124</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2986</v>
+        <v>1.0297</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8874</v>
+        <v>2.3655</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1053</v>
+        <v>2.7514</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2179</v>
+        <v>-0.3859</v>
       </c>
       <c r="G16" t="n">
         <v>0.9841</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4394</v>
+        <v>1.9175</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9831</v>
+        <v>0.6293</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4563</v>
+        <v>1.2883</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.043</v>
+        <v>-0.3459</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2587</v>
+        <v>-1.467</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2158</v>
+        <v>1.1212</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6625</v>
+        <v>-0.3164</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1598</v>
+        <v>-1.8825</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5027</v>
+        <v>1.566</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6685</v>
+        <v>0.4984</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8808</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5493</v>
+        <v>1.3618</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9941</v>
+        <v>-0.8148</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0406</v>
+        <v>-1.0191</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9534</v>
+        <v>0.2042</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0972</v>
+        <v>1.1303</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4787</v>
+        <v>0.3541</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6185</v>
+        <v>0.7762</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5475</v>
+        <v>-0.7684</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.467</v>
+        <v>-0.8588</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9195</v>
+        <v>0.0905</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3164</v>
+        <v>-0.7743</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8825</v>
+        <v>-1.0888</v>
       </c>
       <c r="I18" t="n">
-        <v>1.566</v>
+        <v>0.3145</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4984</v>
+        <v>-0.7527</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.7527</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3618</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8148</v>
+        <v>-0.0216</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0191</v>
+        <v>-0.3361</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2042</v>
+        <v>0.3145</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9287</v>
+        <v>0.0059</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3541</v>
+        <v>-0.1061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5746</v>
+        <v>0.112</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9535</v>
+        <v>-0.8334</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9768</v>
+        <v>0.3151</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0232</v>
+        <v>-1.1485</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7743</v>
+        <v>-2.6625</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0888</v>
+        <v>-0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3145</v>
+        <v>-2.5027</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7527</v>
+        <v>-0.6685</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7527</v>
+        <v>0.8808</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.5493</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0216</v>
+        <v>-1.9941</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3361</v>
+        <v>-1.0406</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>-0.9534</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1792</v>
+        <v>1.2208</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.5351</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0448</v>
+        <v>0.6858</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3702</v>
+        <v>-1.5725</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.725</v>
+        <v>-0.9609</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6452</v>
+        <v>-0.6116</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3338</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6594</v>
+        <v>0.4571</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4705</v>
+        <v>0.5041</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4303</v>
+        <v>-1.5921</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1415</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.5718</v>
+        <v>-1.0755</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.978</v>
+        <v>-1.0124</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5581</v>
+        <v>-0.2629</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.536</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>2.214</v>
+        <v>-0.3477</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9564</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2576</v>
+        <v>-0.4317</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.192</v>
+        <v>-0.6647</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3983</v>
+        <v>-0.3469</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7937</v>
+        <v>-0.3178</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4059</v>
+        <v>0.0286</v>
       </c>
       <c r="T21" t="n">
-        <v>2.0331</v>
+        <v>-0.1689</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3728</v>
+        <v>0.1975</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4665</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9796</v>
+        <v>-2.7573</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.9756</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1091</v>
+        <v>-0.7817</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0124</v>
+        <v>-2.5746</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2629</v>
+        <v>-0.9484</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.6262</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3477</v>
+        <v>-1.8381</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.2654</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4317</v>
+        <v>-1.5727</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6647</v>
+        <v>-0.7365</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3469</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3178</v>
+        <v>-0.0535</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3589</v>
+        <v>-0.1828</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5228</v>
+        <v>-0.1375</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1639</v>
+        <v>-0.0452</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0604</v>
+        <v>-2.8615</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2115</v>
+        <v>2.08</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.849</v>
+        <v>-4.9415</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5746</v>
+        <v>-1.978</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9484</v>
+        <v>0.5581</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6262</v>
+        <v>-2.536</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8381</v>
+        <v>2.214</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2654</v>
+        <v>1.9564</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5727</v>
+        <v>0.2576</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7365</v>
+        <v>-4.192</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.3983</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0535</v>
+        <v>-2.7937</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4859</v>
+        <v>1.9746</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3734</v>
+        <v>0.9715</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1125</v>
+        <v>1.0031</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3159</v>
+        <v>-4.1307</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.343</v>
+        <v>-0.225</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9729</v>
+        <v>-3.9057</v>
       </c>
       <c r="G24" t="n">
         <v>0.7655</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.022</v>
+        <v>0.1632</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1942</v>
+        <v>0.2614</v>
       </c>
       <c r="V24" t="n">
         <v>-5.7553</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8276</v>
+        <v>-4.7997</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7842</v>
+        <v>-0.7226</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0434</v>
+        <v>-4.077</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7256</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7103</v>
+        <v>0.3176</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1123</v>
+        <v>-0.0507</v>
       </c>
       <c r="U25" t="n">
-        <v>0.402</v>
+        <v>0.3684</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8218</v>
+        <v>-7.5194</v>
       </c>
       <c r="E26" t="n">
         <v>-5.4639</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3579</v>
+        <v>-2.0555</v>
       </c>
       <c r="G26" t="n">
         <v>-4.5404</v>
@@ -2482,13 +2482,13 @@
         <v>0.9278</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5715</v>
+        <v>0.874</v>
       </c>
       <c r="T26" t="n">
         <v>0.4525</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1191</v>
+        <v>0.4215</v>
       </c>
       <c r="V26" t="n">
         <v>-0.1418</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.3347</v>
+        <v>-19.3348</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.6279</v>
+        <v>-1.627699999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.707</v>
+        <v>-17.7068</v>
       </c>
       <c r="G27" t="n">
         <v>-12.4882</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.5545</v>
+        <v>-3.554500000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-8.933699999999998</v>
+        <v>-8.9337</v>
       </c>
       <c r="J27" t="n">
-        <v>8.114700000000001</v>
+        <v>8.114699999999999</v>
       </c>
       <c r="K27" t="n">
         <v>5.9579</v>
@@ -2560,13 +2560,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>9.849099999999998</v>
+        <v>9.848900000000002</v>
       </c>
       <c r="T27" t="n">
         <v>3.2465</v>
       </c>
       <c r="U27" t="n">
-        <v>6.602800000000001</v>
+        <v>6.6028</v>
       </c>
       <c r="V27" t="n">
         <v>-8.5776</v>
